--- a/forms/trg/Formulir_TRG_dreams.xlsx
+++ b/forms/trg/Formulir_TRG_dreams.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Yulia Yusrini Djabir, M.BMSc, M.Si, PhD, Apt</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -955,7 +959,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -992,7 +996,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1033,7 +1037,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1070,7 +1074,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1111,7 +1115,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1152,7 +1156,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1193,7 +1197,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1230,7 +1234,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1271,7 +1275,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1312,7 +1316,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1349,7 +1353,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1382,7 +1386,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1415,7 +1419,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1444,7 +1448,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1477,7 +1481,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1510,7 +1514,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1551,7 +1555,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1588,7 +1592,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1629,7 +1633,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1666,7 +1670,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
